--- a/docs/就職活動メモシステム.データ設計書.xlsx
+++ b/docs/就職活動メモシステム.データ設計書.xlsx
@@ -3945,7 +3945,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>STRING（文字列型）／NUMERIC（数値型）／MEMO（メモ型）／CHECKBOX（チェックボックス）</t>
+          <t>STRING（文字列型）／NUMERIC（数値型）／MEMO（メモ型）／CHECKBOX（チェックボックス）／DATE（日付型）</t>
         </is>
       </c>
     </row>
